--- a/Config/Datas/Tables/g_关卡规则_StageRuleConfig.xlsx
+++ b/Config/Datas/Tables/g_关卡规则_StageRuleConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbStageRule" sheetId="1" r:id="R3491fe640ea341b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbStageRule" sheetId="1" r:id="R2a6cde5bd8274246"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -379,6 +379,9 @@
       <x:c r="J1" s="7" t="str">
         <x:v>randomSeed</x:v>
       </x:c>
+      <x:c r="K1" t="str">
+        <x:v>runEventIds</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="9" t="str">
@@ -410,6 +413,9 @@
       </x:c>
       <x:c r="J2" s="9" t="str">
         <x:v>int</x:v>
+      </x:c>
+      <x:c r="K2" t="str">
+        <x:v>(list#sep=;),int#ref=TbRunEvent</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
@@ -425,6 +431,7 @@
       <x:c r="H3" s="11"/>
       <x:c r="I3" s="11"/>
       <x:c r="J3" s="11"/>
+      <x:c r="K3"/>
     </x:row>
     <x:row r="4" ht="54" customHeight="1">
       <x:c r="A4" s="13" t="str">
@@ -457,6 +464,9 @@
       <x:c r="J4" s="13" t="str">
         <x:v>确定性随机种子</x:v>
       </x:c>
+      <x:c r="K4" t="str">
+        <x:v>按计划顺序的局内事件</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="5"/>
@@ -479,13 +489,74 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H5" s="5" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I5" s="5" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J5" s="5" t="n">
         <x:v>20260905</x:v>
+      </x:c>
+      <x:c r="K5" t="str">
+        <x:v>53001;53002;53003;53004;53005;53006;53007;53008;53009;53010;53011;53012</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="B6" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C6" t="n">
+        <x:v>240000</x:v>
+      </x:c>
+      <x:c r="D6" t="n">
+        <x:v>240000</x:v>
+      </x:c>
+      <x:c r="E6" t="str">
+        <x:v>101;102;103</x:v>
+      </x:c>
+      <x:c r="F6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I6" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="J6" t="n">
+        <x:v>20261026</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="B7" t="n">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C7" t="n">
+        <x:v>240000</x:v>
+      </x:c>
+      <x:c r="D7" t="n">
+        <x:v>240000</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>101;102;103</x:v>
+      </x:c>
+      <x:c r="F7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H7" t="n">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="I7" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="J7" t="n">
+        <x:v>20261026</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
